--- a/TMS_Staff_Resource_File.xlsx
+++ b/TMS_Staff_Resource_File.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdemmler\Documents\TMS Staff Resources\Working Version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A622AD9-96AC-4DE6-879D-36D6E1DB6FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C94BC2-4F70-4898-A80C-508B4167B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="943" xr2:uid="{E6363EE6-C1C9-4838-BB78-1A770D1612FC}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3700" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3689" uniqueCount="347">
   <si>
     <t>Monday</t>
   </si>
@@ -12122,7 +12122,7 @@
         <v>28</v>
       </c>
       <c r="B2" s="38">
-        <v>46231</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -59233,40 +59233,40 @@
         <v>0.3125</v>
       </c>
       <c r="J23" s="15">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>11</v>
       </c>
       <c r="L23" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M23" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="15">
         <v>0.3125</v>
       </c>
-      <c r="M23" s="15">
-        <v>0.4375</v>
-      </c>
-      <c r="N23" s="17" t="s">
+      <c r="P23" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q23" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O23" s="15">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="P23" s="15">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="Q23" s="17" t="s">
-        <v>23</v>
-      </c>
       <c r="R23" s="15">
-        <v>0.35416666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S23" s="15">
-        <v>0.72916666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="T23" s="17" t="s">
         <v>23</v>
       </c>
       <c r="U23" s="15">
-        <v>0.3125</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="V23" s="15">
         <v>0.375</v>
@@ -59287,7 +59287,7 @@
       <c r="G24" s="15"/>
       <c r="H24" s="17"/>
       <c r="I24" s="15">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="J24" s="15">
         <v>0.72916666666666663</v>
@@ -59295,15 +59295,9 @@
       <c r="K24" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="L24" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="M24" s="15">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>11</v>
-      </c>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="17"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="17"/>
@@ -59314,7 +59308,7 @@
         <v>0.5</v>
       </c>
       <c r="V24" s="15">
-        <v>0.64583333333333337</v>
+        <v>0.70833333333333337</v>
       </c>
       <c r="W24" s="17" t="s">
         <v>11</v>
@@ -59435,19 +59429,19 @@
       <c r="N29" s="64"/>
       <c r="O29" s="62" cm="1">
         <f t="array" ref="O29">SUM((P23:P27-O23:O27)*24)</f>
-        <v>8.9999999999999982</v>
+        <v>8.5</v>
       </c>
       <c r="P29" s="63"/>
       <c r="Q29" s="64"/>
       <c r="R29" s="62" cm="1">
         <f t="array" ref="R29">SUM((S23:S27-R23:R27)*24)</f>
-        <v>8.9999999999999982</v>
+        <v>8.5</v>
       </c>
       <c r="S29" s="63"/>
       <c r="T29" s="64"/>
       <c r="U29" s="62" cm="1">
         <f t="array" ref="U29">SUM((V23:V27-U23:U27)*24)</f>
-        <v>5.0000000000000009</v>
+        <v>7</v>
       </c>
       <c r="V29" s="63"/>
       <c r="W29" s="64"/>
@@ -59576,7 +59570,7 @@
       </c>
       <c r="C33" s="68">
         <f>SUM(C29:W29)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D33" s="68"/>
       <c r="E33" s="68"/>
@@ -59748,34 +59742,34 @@
         <v>0.3125</v>
       </c>
       <c r="J38" s="15">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="K38" s="17" t="s">
         <v>11</v>
       </c>
       <c r="L38" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M38" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" s="15">
         <v>0.3125</v>
       </c>
-      <c r="M38" s="15">
-        <v>0.4375</v>
-      </c>
-      <c r="N38" s="17" t="s">
+      <c r="P38" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q38" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O38" s="15">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="P38" s="15">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="Q38" s="17" t="s">
-        <v>23</v>
-      </c>
       <c r="R38" s="15">
-        <v>0.35416666666666669</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S38" s="15">
-        <v>0.72916666666666663</v>
+        <v>0.6875</v>
       </c>
       <c r="T38" s="17" t="s">
         <v>23</v>
@@ -59796,7 +59790,7 @@
       <c r="G39" s="15"/>
       <c r="H39" s="17"/>
       <c r="I39" s="15">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="J39" s="15">
         <v>0.72916666666666663</v>
@@ -59804,15 +59798,9 @@
       <c r="K39" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="M39" s="15">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="N39" s="17" t="s">
-        <v>11</v>
-      </c>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="17"/>
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="17"/>
@@ -59939,13 +59927,13 @@
       <c r="N44" s="64"/>
       <c r="O44" s="62" cm="1">
         <f t="array" ref="O44">SUM((P38:P42-O38:O42)*24)</f>
-        <v>8.9999999999999982</v>
+        <v>8.5</v>
       </c>
       <c r="P44" s="63"/>
       <c r="Q44" s="64"/>
       <c r="R44" s="62" cm="1">
         <f t="array" ref="R44">SUM((S38:S42-R38:R42)*24)</f>
-        <v>8.9999999999999982</v>
+        <v>8.5</v>
       </c>
       <c r="S44" s="63"/>
       <c r="T44" s="64"/>
@@ -60082,7 +60070,7 @@
       </c>
       <c r="C48" s="68">
         <f>SUM(C44:W44)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D48" s="68"/>
       <c r="E48" s="68"/>
@@ -60458,7 +60446,7 @@
           <x14:formula1>
             <xm:f>FormTools!$A$1:$A$48</xm:f>
           </x14:formula1>
-          <xm:sqref>R38:S42 C23:D27 F23:G27 I23:J27 L23:M27 R23:S27 I38:J42 U38:V42 C38:D42 F38:G42 L38:M42 O38:P42 O23:P27 U23:V27</xm:sqref>
+          <xm:sqref>R38:S42 C23:D27 F23:G27 I23:J27 L23:M27 R23:S27 U23:V27 U38:V42 C38:D42 F38:G42 L38:M42 O38:P42 O23:P27 I38:J42</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -61161,46 +61149,46 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="J23" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L23" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="M23" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O23" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="P23" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="Q23" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="R23" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="S23" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="U23" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="V23" s="15">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="W23" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="X23" s="7"/>
     </row>
@@ -61214,51 +61202,21 @@
       <c r="F24" s="16"/>
       <c r="G24" s="15"/>
       <c r="H24" s="17"/>
-      <c r="I24" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J24" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="M24" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O24" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="P24" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="Q24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R24" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="S24" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="T24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="U24" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="V24" s="15">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="W24" s="17" t="s">
-        <v>23</v>
-      </c>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="17"/>
       <c r="X24" s="7"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
@@ -61688,37 +61646,37 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="J38" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L38" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="M38" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O38" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="P38" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="Q38" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="R38" s="15">
         <v>0.33333333333333331</v>
       </c>
       <c r="S38" s="15">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="T38" s="17" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="U38" s="15"/>
       <c r="V38" s="15"/>
@@ -61735,42 +61693,18 @@
       <c r="F39" s="16"/>
       <c r="G39" s="15"/>
       <c r="H39" s="17"/>
-      <c r="I39" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="J39" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="K39" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="M39" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="N39" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="P39" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="Q39" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R39" s="15">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="S39" s="15">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="T39" s="17" t="s">
-        <v>23</v>
-      </c>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="17"/>
       <c r="U39" s="15"/>
       <c r="V39" s="15"/>
       <c r="W39" s="17"/>
@@ -62373,7 +62307,7 @@
           <x14:formula1>
             <xm:f>FormTools!$A$1:$A$48</xm:f>
           </x14:formula1>
-          <xm:sqref>I38:J42 C23:D27 F23:G27 I23:J27 R23:S27 L23:M27 R38:S42 L38:M42 C38:D42 F38:G42 O38:P42 O23:P27 U38:V42 U23:V27</xm:sqref>
+          <xm:sqref>R23:S27 C23:D27 F23:G27 I23:J27 O23:P27 U23:V27 O38:P42 I38:J42 C38:D42 F38:G42 L38:M42 L23:M27 U38:V42 R38:S42</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -65509,7 +65443,7 @@
         <v>0.5</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O38" s="15">
         <v>0.33333333333333331</v>
@@ -65560,7 +65494,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O39" s="15">
         <v>0.52083333333333337</v>
